--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/IOWA_2020.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2020/IOWA_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D578"/>
+  <dimension ref="A1:D572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Francisco de los Romo</t>
+          <t>San Francisco De Los Romo</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -592,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C17">
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -696,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Marqués de Comillas</t>
+          <t>Marqués De Comillas</t>
         </is>
       </c>
       <c r="C25">
@@ -709,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C26">
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Cusihuiriachi</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -948,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C44">
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -974,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -987,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -1000,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1013,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Satevó</t>
@@ -1026,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1039,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C51">
@@ -1052,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1083,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1096,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Nava</t>
@@ -1109,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1122,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>San Buenaventura</t>
@@ -1135,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C58">
@@ -1148,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1174,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1205,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1218,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1231,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1244,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1259,7 +1549,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1275,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1288,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1327,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1340,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1353,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1366,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1379,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1392,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1405,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1418,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1449,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1462,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1475,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1488,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1501,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -1514,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1527,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Indé</t>
@@ -1540,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1553,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1566,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Nuevo Ideal</t>
@@ -1579,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1592,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C92">
@@ -1605,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -1631,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>San Pedro del Gallo</t>
+          <t>San Pedro Del Gallo</t>
         </is>
       </c>
       <c r="C95">
@@ -1644,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Tamazula</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -1683,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1698,7 +2143,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1714,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C101">
@@ -1727,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1740,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Apaxco</t>
@@ -1753,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Atizapán</t>
@@ -1766,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C105">
@@ -1779,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1792,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1805,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Chiconcuac</t>
@@ -1818,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C109">
@@ -1831,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C110">
@@ -1844,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1857,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C112">
@@ -1870,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -1896,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C115">
@@ -1909,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Soyaniquilpan de Juárez</t>
+          <t>Soyaniquilpan De Juárez</t>
         </is>
       </c>
       <c r="C116">
@@ -1922,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1935,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1948,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Temascalapa</t>
@@ -1961,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1974,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Teotihuacán</t>
@@ -1987,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -2000,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C123">
@@ -2013,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2026,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2039,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Villa de Allende</t>
+          <t>Villa De Allende</t>
         </is>
       </c>
       <c r="C126">
@@ -2052,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Villa Guerero</t>
@@ -2065,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -2078,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2093,7 +2683,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2109,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2122,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -2135,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C133">
@@ -2148,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C134">
@@ -2161,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2174,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2187,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -2200,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -2213,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -2226,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2239,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C141">
@@ -2252,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2265,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>León</t>
@@ -2278,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2291,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2304,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2317,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Purísima del Rincón</t>
+          <t>Purísima Del Rincón</t>
         </is>
       </c>
       <c r="C147">
@@ -2330,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -2343,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2356,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2369,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2382,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C152">
@@ -2395,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C153">
@@ -2408,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C154">
@@ -2421,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C155">
@@ -2434,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -2447,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C157">
@@ -2460,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2498,7 +3228,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C160">
@@ -2509,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C161">
@@ -2522,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -2535,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2548,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C164">
@@ -2561,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C165">
@@ -2574,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -2587,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -2600,9 +3365,14 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Buenavista de Cuéllar</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C168">
@@ -2613,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C169">
@@ -2626,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C170">
@@ -2639,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -2652,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -2665,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C173">
@@ -2678,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C174">
@@ -2691,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2704,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -2717,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -2730,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -2743,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C179">
@@ -2756,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -2769,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C181">
@@ -2782,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2795,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C183">
@@ -2808,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -2821,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2834,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -2847,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -2860,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -2873,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2886,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2899,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -2912,9 +3797,14 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C192">
@@ -2925,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2938,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2951,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -2964,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C196">
@@ -2977,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C197">
@@ -2990,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -3003,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3016,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3047,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -3060,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Agua Blanca de Iturbide</t>
+          <t>Agua Blanca De Iturbide</t>
         </is>
       </c>
       <c r="C203">
@@ -3073,9 +4013,14 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C204">
@@ -3086,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -3099,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C206">
@@ -3112,9 +4067,14 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Huasca de Ocampo</t>
+          <t>Huasca De Ocampo</t>
         </is>
       </c>
       <c r="C207">
@@ -3125,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C208">
@@ -3138,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -3151,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3164,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -3177,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -3190,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mineral del Chico</t>
+          <t>Mineral Del Chico</t>
         </is>
       </c>
       <c r="C213">
@@ -3203,9 +4193,14 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C214">
@@ -3216,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>San Bartolo Tutotepec</t>
@@ -3229,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -3242,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C217">
@@ -3255,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Zempoala</t>
@@ -3268,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -3281,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3301,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Acatlán de Juárez</t>
+          <t>Acatlán De Juárez</t>
         </is>
       </c>
       <c r="C221">
@@ -3312,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -3325,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -3338,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Atemajac de Brizuela</t>
+          <t>Atemajac De Brizuela</t>
         </is>
       </c>
       <c r="C224">
@@ -3351,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Atengo</t>
@@ -3364,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C226">
@@ -3377,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -3390,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -3403,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -3416,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -3429,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -3442,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -3455,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Guachinango</t>
@@ -3468,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3481,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Hostotipaquillo</t>
@@ -3494,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C236">
@@ -3507,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -3520,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Jamay</t>
@@ -3533,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -3546,9 +4661,14 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Jilotlán de los Dolores</t>
+          <t>Jilotlán De Los Dolores</t>
         </is>
       </c>
       <c r="C240">
@@ -3559,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -3572,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -3585,9 +4715,14 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C243">
@@ -3598,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C244">
@@ -3611,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -3624,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Mascota</t>
@@ -3637,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Mixtlán</t>
@@ -3650,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -3663,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -3676,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -3689,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -3702,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C252">
@@ -3715,9 +4895,14 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C253">
@@ -3728,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -3741,9 +4931,14 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C255">
@@ -3754,9 +4949,14 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>San Sebastián del Oeste</t>
+          <t>San Sebastián Del Oeste</t>
         </is>
       </c>
       <c r="C256">
@@ -3767,9 +4967,14 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Santa María de los Ángeles</t>
+          <t>Santa María De Los Ángeles</t>
         </is>
       </c>
       <c r="C257">
@@ -3780,9 +4985,14 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C258">
@@ -3793,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Tapalpa</t>
@@ -3806,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -3819,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -3832,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Tenamaxtlán</t>
@@ -3845,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C263">
@@ -3858,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -3871,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C265">
@@ -3884,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -3897,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -3910,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -3923,9 +5183,14 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Unión de San Antonio</t>
+          <t>Unión De San Antonio</t>
         </is>
       </c>
       <c r="C269">
@@ -3936,9 +5201,14 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C270">
@@ -3949,9 +5219,14 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Valle de Juárez</t>
+          <t>Valle De Juárez</t>
         </is>
       </c>
       <c r="C271">
@@ -3962,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Yahualica de González Gallo</t>
+          <t>Yahualica De González Gallo</t>
         </is>
       </c>
       <c r="C272">
@@ -3975,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C273">
@@ -3988,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -4001,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C275">
@@ -4014,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -4027,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4058,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Aguililla</t>
@@ -4071,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Angamacutiro</t>
@@ -4084,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4097,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -4110,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -4123,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -4136,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -4149,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C286">
@@ -4162,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -4175,9 +5525,14 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Cojumatlán de Régules</t>
+          <t>Cojumatlán De Régules</t>
         </is>
       </c>
       <c r="C288">
@@ -4188,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -4201,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -4214,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -4227,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Ecuandureo</t>
@@ -4240,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -4253,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -4266,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4279,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -4292,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -4305,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Ixtlán</t>
@@ -4318,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Jacona</t>
@@ -4331,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -4344,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>José Sixto Verduzco</t>
@@ -4357,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -4370,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -4379,10 +5809,15 @@
         <v>17</v>
       </c>
       <c r="D303">
-        <v>0.009703196347031963</v>
+        <v>0.009703196347031965</v>
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4396,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4409,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Madero</t>
@@ -4422,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -4435,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4448,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4461,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Nuevo Urecho</t>
@@ -4474,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Numarán</t>
@@ -4487,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -4500,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Pajacuarán</t>
@@ -4513,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -4526,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -4539,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Penjamillo</t>
@@ -4552,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -4565,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -4578,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -4591,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -4604,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -4617,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -4630,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -4643,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -4656,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -4669,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -4682,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -4695,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -4708,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -4721,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -4734,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4747,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -4760,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -4773,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -4786,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -4799,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -4812,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -4825,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -4838,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -4851,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -4864,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4895,9 +6515,14 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Coatlán del Río</t>
+          <t>Coatlán Del Río</t>
         </is>
       </c>
       <c r="C343">
@@ -4908,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -4921,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -4934,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4947,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Jiutepec</t>
@@ -4960,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -4973,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -4986,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Ocuituco</t>
@@ -4999,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -5012,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -5025,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C353">
@@ -5038,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -5051,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -5064,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -5077,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5108,9 +6803,14 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C359">
@@ -5121,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -5134,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -5147,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -5160,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -5173,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -5186,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -5199,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5212,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5243,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>General Terán</t>
@@ -5256,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MonteMorelos</t>
+          <t>Montemorelos</t>
         </is>
       </c>
       <c r="C370">
@@ -5269,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -5282,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Rayones</t>
@@ -5295,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C373">
@@ -5308,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5328,7 +7098,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C375">
@@ -5339,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Candelaria Loxicha</t>
@@ -5352,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -5365,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C378">
@@ -5378,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -5391,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C380">
@@ -5404,9 +7199,14 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C381">
@@ -5417,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>San Agustín Amatengo</t>
@@ -5430,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>San Agustín Atenango</t>
@@ -5443,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -5456,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>San Antonino el Alto</t>
+          <t>San Antonino El Alto</t>
         </is>
       </c>
       <c r="C385">
@@ -5469,9 +7289,14 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>San Felipe Jalapa de Díaz</t>
+          <t>San Felipe Jalapa De Díaz</t>
         </is>
       </c>
       <c r="C386">
@@ -5482,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5495,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -5508,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -5521,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -5534,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -5547,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>San Juan Yucuita</t>
@@ -5560,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>San Lucas Ojitlán</t>
@@ -5573,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>San Miguel Chimalapa</t>
@@ -5586,9 +7451,14 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>San Miguel del Puerto</t>
+          <t>San Miguel Del Puerto</t>
         </is>
       </c>
       <c r="C395">
@@ -5599,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>San Miguel Mixtepec</t>
@@ -5612,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -5625,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>San Miguel Quetzaltepec</t>
@@ -5638,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -5651,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -5664,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>San Vicente Coatlán</t>
@@ -5677,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -5690,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Santa Cruz Nundaco</t>
@@ -5703,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -5716,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Santa María Yolotepec</t>
@@ -5729,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -5742,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -5755,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -5768,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Santiago Tamazola</t>
@@ -5781,6 +7721,11 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -5794,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5807,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Trinidad Zaachila</t>
@@ -5820,9 +7775,14 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C413">
@@ -5833,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5864,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -5877,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -5890,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Chiconcuautla</t>
@@ -5903,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -5916,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -5929,9 +7919,14 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C421">
@@ -5942,9 +7937,14 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C422">
@@ -5955,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -5968,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -5981,9 +7991,14 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C425">
@@ -5994,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -6007,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -6020,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -6033,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -6046,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -6059,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6090,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -6103,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Pedro Escobedo</t>
@@ -6116,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6129,9 +8189,14 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C436">
@@ -6142,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6173,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Charcas</t>
@@ -6186,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -6199,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6212,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -6225,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Matlapa</t>
@@ -6238,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -6251,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -6264,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -6277,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6290,9 +8405,14 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C448">
@@ -6303,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -6316,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -6329,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -6342,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -6355,9 +8495,14 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C453">
@@ -6368,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6399,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -6412,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -6425,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -6438,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -6451,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6482,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Huatabampo</t>
@@ -6495,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -6508,9 +8693,14 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C464">
@@ -6521,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -6534,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6565,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -6578,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -6591,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6622,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Ciudad Madero</t>
@@ -6635,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -6648,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>González</t>
@@ -6661,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -6674,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Nuevo Laredo</t>
@@ -6687,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -6700,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Padilla</t>
@@ -6713,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -6726,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -6739,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -6752,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -6765,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6796,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -6809,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Teolocholco</t>
@@ -6822,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -6835,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6866,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Agua Dulce</t>
@@ -6879,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Alpatláhuac</t>
@@ -6892,9 +9197,14 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Alto Lucero de Gutiérrez Barrios</t>
+          <t>Alto Lucero De Gutiérrez Barrios</t>
         </is>
       </c>
       <c r="C492">
@@ -6905,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -6918,6 +9233,11 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -6931,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -6944,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Camerino Z. Mendoza</t>
@@ -6957,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -6970,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Cerro Azul</t>
@@ -6983,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -6996,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -7009,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -7022,9 +9377,14 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C502">
@@ -7035,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Cotaxtla</t>
@@ -7048,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -7061,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -7074,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -7087,9 +9467,14 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C507">
@@ -7100,6 +9485,11 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
           <t>Jalcomulco</t>
@@ -7113,6 +9503,11 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -7126,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -7139,9 +9539,14 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C511">
@@ -7152,6 +9557,11 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -7165,9 +9575,14 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C513">
@@ -7178,9 +9593,14 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Medellín de Bravo</t>
+          <t>Medellín De Bravo</t>
         </is>
       </c>
       <c r="C514">
@@ -7191,6 +9611,11 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -7204,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -7217,6 +9647,11 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -7230,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -7243,6 +9683,11 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -7256,6 +9701,11 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -7269,9 +9719,14 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C521">
@@ -7282,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -7295,9 +9755,14 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C523">
@@ -7308,6 +9773,11 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Pueblo Viejo</t>
@@ -7321,6 +9791,11 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -7334,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -7347,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -7360,9 +9845,14 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C528">
@@ -7373,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>Tepetlán</t>
@@ -7386,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Tepetzintla</t>
@@ -7399,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -7412,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -7425,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -7438,9 +9953,14 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Vega de Alatorre</t>
+          <t>Vega De Alatorre</t>
         </is>
       </c>
       <c r="C534">
@@ -7451,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -7464,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -7477,6 +10007,11 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>Yecuatla</t>
@@ -7490,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -7503,6 +10043,11 @@
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -7516,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7547,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7578,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>Calera</t>
@@ -7591,9 +10151,14 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Concepción del Oro</t>
+          <t>Concepción Del Oro</t>
         </is>
       </c>
       <c r="C545">
@@ -7604,9 +10169,14 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>El Plateado de Joaquín Amaro</t>
+          <t>El Plateado De Joaquín Amaro</t>
         </is>
       </c>
       <c r="C546">
@@ -7617,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -7626,10 +10201,15 @@
         <v>17</v>
       </c>
       <c r="D547">
-        <v>0.009703196347031963</v>
+        <v>0.009703196347031965</v>
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -7643,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -7656,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -7669,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -7682,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -7695,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -7708,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -7721,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Melchor Ocampo</t>
@@ -7734,9 +10349,14 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Mezquital del Oro</t>
+          <t>Mezquital Del Oro</t>
         </is>
       </c>
       <c r="C556">
@@ -7747,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -7760,6 +10385,11 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -7773,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -7786,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -7799,6 +10439,11 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -7812,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -7825,6 +10475,11 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
           <t>Tabasco</t>
@@ -7838,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -7851,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -7864,9 +10529,14 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C566">
@@ -7877,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -7890,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -7903,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -7916,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -7929,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7952,41 +10647,6 @@
       </c>
       <c r="D572">
         <v>1</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
